--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858317</v>
       </c>
       <c r="B3" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858321</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858319</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858317</v>
       </c>
       <c r="B3" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858321</v>
       </c>
       <c r="B4" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858319</v>
       </c>
       <c r="B5" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858317</v>
       </c>
       <c r="B3" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858321</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858319</v>
       </c>
       <c r="B5" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858317</v>
       </c>
       <c r="B3" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858321</v>
       </c>
       <c r="B4" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858319</v>
       </c>
       <c r="B5" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858317</v>
       </c>
       <c r="B3" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858321</v>
       </c>
       <c r="B4" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858319</v>
       </c>
       <c r="B5" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42347-2026 artfynd.xlsx
+++ b/artfynd/A 42347-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858320</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136858317</v>
       </c>
       <c r="B3" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136858321</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136858319</v>
       </c>
       <c r="B5" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
